--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20359"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikoz\Documents\GitHub\mesterremek\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3406TAN-01\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C73E85-AFE0-4923-BDAF-54A4A12F80CE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLANs" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
     <sheet name="Router IP" sheetId="4" r:id="rId3"/>
     <sheet name="Device$" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="186">
   <si>
     <t>vendég</t>
   </si>
@@ -582,12 +583,15 @@
   </si>
   <si>
     <t>172.16.20.1/24 ; 2001:20::1/64</t>
+  </si>
+  <si>
+    <t>LM_Factory_w</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;Ft&quot;_-;\-* #,##0.00\ &quot;Ft&quot;_-;_-* &quot;-&quot;??\ &quot;Ft&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;Ft&quot;_-;\-* #,##0\ &quot;Ft&quot;_-;_-* &quot;-&quot;??\ &quot;Ft&quot;_-;_-@_-"/>
@@ -1410,7 +1414,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1802,6 +1806,18 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1814,16 +1830,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2135,25 +2145,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:K100"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:11" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="119" t="s">
         <v>172</v>
       </c>
@@ -2170,7 +2180,7 @@
       <c r="J3" s="120"/>
       <c r="K3" s="121"/>
     </row>
-    <row r="4" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
         <v>175</v>
       </c>
@@ -2201,7 +2211,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>10</v>
       </c>
@@ -2232,7 +2242,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="38">
         <v>20</v>
       </c>
@@ -2263,7 +2273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="38">
         <v>30</v>
       </c>
@@ -2294,7 +2304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="38">
         <v>40</v>
       </c>
@@ -2325,7 +2335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="38">
         <v>50</v>
       </c>
@@ -2350,7 +2360,7 @@
       <c r="J9" s="44"/>
       <c r="K9" s="43"/>
     </row>
-    <row r="10" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="50">
         <v>90</v>
       </c>
@@ -2369,7 +2379,7 @@
       <c r="J10" s="44"/>
       <c r="K10" s="43"/>
     </row>
-    <row r="11" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>101</v>
       </c>
@@ -2388,7 +2398,7 @@
       <c r="J11" s="44"/>
       <c r="K11" s="43"/>
     </row>
-    <row r="12" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="38"/>
       <c r="B12" s="39"/>
       <c r="C12" s="40"/>
@@ -2401,7 +2411,7 @@
       <c r="J12" s="44"/>
       <c r="K12" s="43"/>
     </row>
-    <row r="13" spans="1:11" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="52"/>
       <c r="B13" s="53"/>
       <c r="C13" s="54"/>
@@ -2414,86 +2424,86 @@
       <c r="J13" s="56"/>
       <c r="K13" s="57"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:C3"/>
@@ -2506,25 +2516,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="127" t="s">
         <v>21</v>
       </c>
@@ -2544,7 +2554,7 @@
       <c r="M1" s="125"/>
       <c r="N1" s="126"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
         <v>22</v>
       </c>
@@ -2582,7 +2592,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="130" t="s">
         <v>26</v>
       </c>
@@ -2614,7 +2624,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="130"/>
       <c r="B4" s="4" t="s">
         <v>28</v>
@@ -2646,7 +2656,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="130"/>
       <c r="B5" s="2" t="s">
         <v>29</v>
@@ -2678,7 +2688,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="130"/>
       <c r="B6" s="5" t="s">
         <v>30</v>
@@ -2711,7 +2721,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="130"/>
       <c r="B7" s="2" t="s">
         <v>31</v>
@@ -2745,7 +2755,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="130"/>
       <c r="B8" s="5" t="s">
         <v>32</v>
@@ -2774,10 +2784,10 @@
         <v>10</v>
       </c>
       <c r="N8" s="86" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="130"/>
       <c r="B9" s="2" t="s">
         <v>33</v>
@@ -2805,11 +2815,11 @@
       <c r="M9" s="80">
         <v>20</v>
       </c>
-      <c r="N9" s="142" t="s">
+      <c r="N9" s="137" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="130" t="s">
         <v>40</v>
       </c>
@@ -2841,9 +2851,9 @@
       <c r="M10" s="76">
         <v>20</v>
       </c>
-      <c r="N10" s="143"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N10" s="138"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="130"/>
       <c r="B11" s="3" t="s">
         <v>42</v>
@@ -2871,9 +2881,9 @@
       <c r="M11" s="80">
         <v>20</v>
       </c>
-      <c r="N11" s="143"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N11" s="138"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="130"/>
       <c r="B12" s="5" t="s">
         <v>43</v>
@@ -2901,9 +2911,9 @@
       <c r="M12" s="76">
         <v>20</v>
       </c>
-      <c r="N12" s="143"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N12" s="138"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="130"/>
       <c r="B13" s="3" t="s">
         <v>44</v>
@@ -2931,9 +2941,9 @@
       <c r="M13" s="80">
         <v>20</v>
       </c>
-      <c r="N13" s="143"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N13" s="138"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="130"/>
       <c r="B14" s="5" t="s">
         <v>45</v>
@@ -2961,9 +2971,9 @@
       <c r="M14" s="76">
         <v>20</v>
       </c>
-      <c r="N14" s="143"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N14" s="138"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="130"/>
       <c r="B15" s="3" t="s">
         <v>46</v>
@@ -2991,9 +3001,9 @@
       <c r="M15" s="80">
         <v>20</v>
       </c>
-      <c r="N15" s="143"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N15" s="138"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="130"/>
       <c r="B16" s="5" t="s">
         <v>47</v>
@@ -3021,9 +3031,9 @@
       <c r="M16" s="76">
         <v>20</v>
       </c>
-      <c r="N16" s="143"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N16" s="138"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="130"/>
       <c r="B17" s="3" t="s">
         <v>48</v>
@@ -3051,9 +3061,9 @@
       <c r="M17" s="80">
         <v>20</v>
       </c>
-      <c r="N17" s="144"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N17" s="139"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="130"/>
       <c r="B18" s="5" t="s">
         <v>49</v>
@@ -3089,7 +3099,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="130"/>
       <c r="B19" s="3" t="s">
         <v>50</v>
@@ -3125,7 +3135,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="130"/>
       <c r="B20" s="5" t="s">
         <v>63</v>
@@ -3161,7 +3171,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="130"/>
       <c r="B21" s="3" t="s">
         <v>51</v>
@@ -3197,7 +3207,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="67" t="s">
         <v>94</v>
       </c>
@@ -3235,7 +3245,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
         <v>62</v>
       </c>
@@ -3261,7 +3271,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="68" t="s">
         <v>65</v>
       </c>
@@ -3287,7 +3297,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
         <v>67</v>
       </c>
@@ -3313,7 +3323,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="68" t="s">
         <v>68</v>
       </c>
@@ -3339,7 +3349,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="29" t="s">
         <v>69</v>
       </c>
@@ -3358,8 +3368,20 @@
       <c r="G27" s="128"/>
       <c r="H27" s="128"/>
       <c r="I27" s="129"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K27" t="s">
+        <v>185</v>
+      </c>
+      <c r="L27" s="145" t="s">
+        <v>66</v>
+      </c>
+      <c r="M27" s="146">
+        <v>10</v>
+      </c>
+      <c r="N27" s="86" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
         <v>70</v>
       </c>
@@ -3385,7 +3407,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
         <v>71</v>
       </c>
@@ -3411,7 +3433,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="69" t="s">
         <v>86</v>
       </c>
@@ -3437,14 +3459,14 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="93"/>
       <c r="B33" s="94" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>26</v>
       </c>
@@ -3452,7 +3474,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="95" t="s">
         <v>73</v>
       </c>
@@ -3479,16 +3501,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="116" t="s">
         <v>22</v>
       </c>
@@ -3505,7 +3527,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="96" t="s">
         <v>151</v>
       </c>
@@ -3522,8 +3544,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="139" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="143" t="s">
         <v>142</v>
       </c>
       <c r="B3" s="103" t="s">
@@ -3532,36 +3554,36 @@
       <c r="C3" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="D3" s="140">
+      <c r="D3" s="144">
         <v>200</v>
       </c>
-      <c r="E3" s="141" t="s">
+      <c r="E3" s="140" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="139"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="143"/>
       <c r="B4" s="84" t="s">
         <v>143</v>
       </c>
       <c r="C4" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="D4" s="140"/>
-      <c r="E4" s="141"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="139"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="140"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="143"/>
       <c r="B5" s="103" t="s">
         <v>144</v>
       </c>
       <c r="C5" s="103" t="s">
         <v>154</v>
       </c>
-      <c r="D5" s="140"/>
-      <c r="E5" s="141"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5" s="144"/>
+      <c r="E5" s="140"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
         <v>97</v>
       </c>
@@ -3578,8 +3600,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="139" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="143" t="s">
         <v>145</v>
       </c>
       <c r="B7" s="103" t="s">
@@ -3588,36 +3610,36 @@
       <c r="C7" s="103" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="140">
+      <c r="D7" s="144">
         <v>400</v>
       </c>
-      <c r="E7" s="141">
+      <c r="E7" s="140">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="139"/>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="143"/>
       <c r="B8" s="84" t="s">
         <v>143</v>
       </c>
       <c r="C8" s="84" t="s">
         <v>156</v>
       </c>
-      <c r="D8" s="140"/>
-      <c r="E8" s="141"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="139"/>
+      <c r="D8" s="144"/>
+      <c r="E8" s="140"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="143"/>
       <c r="B9" s="103" t="s">
         <v>144</v>
       </c>
       <c r="C9" s="103" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="140"/>
-      <c r="E9" s="141"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9" s="144"/>
+      <c r="E9" s="140"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
         <v>26</v>
       </c>
@@ -3634,7 +3656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="99" t="s">
         <v>73</v>
       </c>
@@ -3651,8 +3673,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="96" t="s">
         <v>162</v>
       </c>
@@ -3661,16 +3683,16 @@
       </c>
       <c r="C13" s="98"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="137" t="s">
+      <c r="B14" s="141" t="s">
         <v>168</v>
       </c>
-      <c r="C14" s="138"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C14" s="142"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
         <v>164</v>
       </c>
@@ -3679,7 +3701,7 @@
       </c>
       <c r="C15" s="66"/>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="99" t="s">
         <v>165</v>
       </c>
@@ -3702,18 +3724,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F67"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="66.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="66.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="107" t="s">
         <v>22</v>
       </c>
@@ -3733,7 +3755,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>122</v>
       </c>
@@ -3754,7 +3776,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>125</v>
       </c>
@@ -3775,7 +3797,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>127</v>
       </c>
@@ -3796,7 +3818,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>131</v>
       </c>
@@ -3817,7 +3839,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>132</v>
       </c>
@@ -3838,7 +3860,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>133</v>
       </c>
@@ -3859,7 +3881,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>134</v>
       </c>
@@ -3880,7 +3902,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>135</v>
       </c>
@@ -3901,7 +3923,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>138</v>
       </c>
@@ -3922,7 +3944,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>139</v>
       </c>
@@ -3943,7 +3965,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="s">
         <v>140</v>
       </c>
@@ -3959,295 +3981,295 @@
       </c>
       <c r="F12" s="115"/>
     </row>
-    <row r="13" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="10"/>
       <c r="D13" s="9"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="10"/>
       <c r="D14" s="9"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="10"/>
       <c r="D15" s="9"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="10"/>
       <c r="D16" s="9"/>
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="10"/>
       <c r="D17" s="9"/>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="10"/>
       <c r="D18" s="9"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="10"/>
       <c r="D19" s="9"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="10"/>
       <c r="D20" s="9"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="10"/>
       <c r="D21" s="9"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="10"/>
       <c r="D22" s="9"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="10"/>
       <c r="D23" s="9"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="10"/>
       <c r="D24" s="9"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="10"/>
       <c r="D25" s="9"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="10"/>
       <c r="D26" s="9"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="10"/>
       <c r="D27" s="9"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="10"/>
       <c r="D28" s="9"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="10"/>
       <c r="D29" s="9"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="10"/>
       <c r="D30" s="9"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" s="8"/>
       <c r="C31" s="10"/>
       <c r="D31" s="9"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="8"/>
       <c r="C32" s="10"/>
       <c r="D32" s="9"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="9"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="8"/>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="8"/>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="8"/>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="8"/>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="8"/>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" s="8"/>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B66" s="8"/>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B67" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{00000000-0004-0000-0300-000004000000}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{00000000-0004-0000-0300-000005000000}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{00000000-0004-0000-0300-000006000000}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{00000000-0004-0000-0300-000007000000}"/>
+    <hyperlink ref="F10" r:id="rId9" xr:uid="{00000000-0004-0000-0300-000008000000}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{00000000-0004-0000-0300-000009000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" r:id="rId11"/>
